--- a/data/trans_orig/P70B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023</t>
+          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37718</t>
+          <t>40525</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>39320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>40058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68591</t>
+          <t>69257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179053</t>
+          <t>179100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>219045</t>
+          <t>219521</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>174207</t>
+          <t>174955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203837</t>
+          <t>205428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>359320</t>
+          <t>360763</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>412453</t>
+          <t>411736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>105152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143458</t>
+          <t>144892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79792</t>
+          <t>79180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109055</t>
+          <t>107629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193389</t>
+          <t>194285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241900</t>
+          <t>241505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>17580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42500</t>
+          <t>43806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28294</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37737</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>65393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166775</t>
+          <t>166237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204579</t>
+          <t>204584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138677</t>
+          <t>138436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165287</t>
+          <t>165329</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313313</t>
+          <t>315850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359884</t>
+          <t>362469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63007</t>
+          <t>63913</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94963</t>
+          <t>97484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62138</t>
+          <t>62614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87236</t>
+          <t>88015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132506</t>
+          <t>132794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175046</t>
+          <t>174484</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21940</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69333</t>
+          <t>68719</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84106</t>
+          <t>84298</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>307478</t>
+          <t>307598</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>468597</t>
+          <t>460493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35338</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49623</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344812</t>
+          <t>348255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>521744</t>
+          <t>523352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>101752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22146</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>118632</t>
+          <t>117967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33332</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21843</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76486</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121319</t>
+          <t>121542</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58178</t>
+          <t>57516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84045</t>
+          <t>85781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,47 +2600,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>20,18%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>168375</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>142957</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>194377</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>14,54%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>19,77%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>168375</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>144420</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>198165</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>17,12%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>293204</t>
+          <t>295026</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>346950</t>
+          <t>346830</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>225787</t>
+          <t>225180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>262954</t>
+          <t>263040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>535798</t>
+          <t>534538</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>599377</t>
+          <t>598839</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98467</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140660</t>
+          <t>140407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80006</t>
+          <t>78483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111778</t>
+          <t>111150</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186352</t>
+          <t>186383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240805</t>
+          <t>241639</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>34282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>34366</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49833</t>
+          <t>48877</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52677</t>
+          <t>52691</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42785</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87946</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126521</t>
+          <t>127762</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162792</t>
+          <t>162775</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112308</t>
+          <t>109420</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>258717</t>
+          <t>256566</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>220409</t>
+          <t>233243</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>400338</t>
+          <t>398545</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>44689</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>76763</t>
+          <t>74859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234112</t>
+          <t>250817</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>128793</t>
+          <t>128886</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>345645</t>
+          <t>321079</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3565,107 +3565,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44925</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55896</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80901</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3678,107 +3678,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>212875</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132263</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257106</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>233</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138831</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>194212</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>420</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380657</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292344</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>434061</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -3791,107 +3791,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1254560</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1138998</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1488750</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>826519</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694612</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>889327</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2081078</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1936708</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2367154</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -3904,107 +3904,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>403</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>426663</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>277383</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505746</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>502</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>409221</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344281</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>580151</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>905</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>835884</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674277</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>990043</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -4017,690 +4017,120 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1939022</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1939022</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1939022</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439499</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439499</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1439499</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3378520</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3378520</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3378520</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Nada bien</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>44925</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>28348</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>60830</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>35976</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>25671</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>54613</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>80901</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>58823</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>105853</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>No muy bien</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>212875</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>143064</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>256505</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>136415</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>192341</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>380657</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>292161</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>437319</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Bastante bien</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1254560</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1143062</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1487834</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>64,7%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>58,95%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>76,73%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>826519</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>698888</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>887045</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>57,42%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>48,55%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>61,62%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>2081078</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>1946628</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>2397893</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>61,6%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>57,62%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>70,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Muy bien</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>426663</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>279420</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>500224</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>25,8%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>409221</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>344902</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>583410</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>40,53%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>835884</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>657492</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>993700</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>1645</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>1939022</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1939022</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1939022</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>1439499</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>1439499</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1439499</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>3640</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>3378520</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>3378520</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3378520</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A34:A38"/>
     <mergeCell ref="A29:A33"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A24:A28"/>

--- a/data/trans_orig/P70B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Clase-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5578</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11498</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>10907</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>18513</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2236</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11260</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>10841</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>5757</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>19723</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23102</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29076</t>
+          <t>29615</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20986</t>
+          <t>20897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39320</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>52178</t>
+          <t>52152</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40058</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69257</t>
+          <t>68065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>198260</t>
+          <t>212143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179100</t>
+          <t>190976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>219521</t>
+          <t>233753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>189327</t>
+          <t>200364</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>174955</t>
+          <t>184766</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205428</t>
+          <t>215580</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>387588</t>
+          <t>412507</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360763</t>
+          <t>384508</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>411736</t>
+          <t>439529</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>124555</t>
+          <t>142067</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105152</t>
+          <t>122237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144892</t>
+          <t>163634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92879</t>
+          <t>102696</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79180</t>
+          <t>89115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107629</t>
+          <t>118162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>217434</t>
+          <t>244763</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194285</t>
+          <t>220406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241505</t>
+          <t>274701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>351230</t>
+          <t>382078</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351230</t>
+          <t>382078</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>351230</t>
+          <t>382078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>316811</t>
+          <t>338252</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316811</t>
+          <t>338252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316811</t>
+          <t>338252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>668041</t>
+          <t>720330</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>668041</t>
+          <t>720330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>668041</t>
+          <t>720330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,22 +1294,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>30840</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43806</t>
+          <t>45424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>20424</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29280</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>51264</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65393</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>186239</t>
+          <t>198316</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166237</t>
+          <t>178006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204584</t>
+          <t>217263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152344</t>
+          <t>165264</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138436</t>
+          <t>150736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165329</t>
+          <t>180273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>338582</t>
+          <t>363580</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315850</t>
+          <t>338507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>362469</t>
+          <t>384926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78987</t>
+          <t>82510</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63913</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97484</t>
+          <t>101138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73919</t>
+          <t>81739</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62614</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>94376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>152905</t>
+          <t>164248</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132794</t>
+          <t>144925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174484</t>
+          <t>187224</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>303018</t>
+          <t>320404</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>303018</t>
+          <t>320404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>303018</t>
+          <t>320404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>252245</t>
+          <t>273521</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252245</t>
+          <t>273521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252245</t>
+          <t>273521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>555262</t>
+          <t>593925</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>555262</t>
+          <t>593925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>555262</t>
+          <t>593925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30970</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68719</t>
+          <t>45936</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43156</t>
+          <t>45842</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>34814</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84298</t>
+          <t>59687</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>402641</t>
+          <t>178726</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>307598</t>
+          <t>160253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>460493</t>
+          <t>195410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>49472</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35111</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49281</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>445288</t>
+          <t>228199</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348255</t>
+          <t>209931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>523352</t>
+          <t>246744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46450</t>
+          <t>51125</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>37059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101752</t>
+          <t>67706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>61747</t>
+          <t>67777</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>54016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117967</t>
+          <t>83743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>486743</t>
+          <t>269434</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>486743</t>
+          <t>269434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>486743</t>
+          <t>269434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72488</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72488</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72488</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>559231</t>
+          <t>351676</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>559231</t>
+          <t>351676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>559231</t>
+          <t>351676</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25688</t>
+          <t>31849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49481</t>
+          <t>60860</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>97653</t>
+          <t>101460</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75250</t>
+          <t>80513</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121542</t>
+          <t>124873</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>70722</t>
+          <t>77288</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57516</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85781</t>
+          <t>92556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>168375</t>
+          <t>178747</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142957</t>
+          <t>153952</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194377</t>
+          <t>206610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>321841</t>
+          <t>358841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>295026</t>
+          <t>331822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>346830</t>
+          <t>386563</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>245153</t>
+          <t>279693</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>225180</t>
+          <t>259041</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>263040</t>
+          <t>298189</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>566994</t>
+          <t>638534</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>534538</t>
+          <t>607601</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>598839</t>
+          <t>674423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>117672</t>
+          <t>131512</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97222</t>
+          <t>109335</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140407</t>
+          <t>156616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>94684</t>
+          <t>104334</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78483</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111150</t>
+          <t>122796</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>212356</t>
+          <t>235846</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186383</t>
+          <t>209118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241639</t>
+          <t>268321</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>558119</t>
+          <t>619287</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558119</t>
+          <t>619287</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>558119</t>
+          <t>619287</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>425107</t>
+          <t>477743</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>425107</t>
+          <t>477743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>425107</t>
+          <t>477743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>983226</t>
+          <t>1097030</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>983226</t>
+          <t>1097030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>983226</t>
+          <t>1097030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34282</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>31566</t>
+          <t>39244</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48877</t>
+          <t>56741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>35769</t>
+          <t>42533</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52691</t>
+          <t>55477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>67335</t>
+          <t>81777</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43633</t>
+          <t>64259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>100966</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>145579</t>
+          <t>179070</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127762</t>
+          <t>156775</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162775</t>
+          <t>197215</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>197048</t>
+          <t>194816</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109420</t>
+          <t>178917</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>256566</t>
+          <t>210807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>342626</t>
+          <t>373885</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>233243</t>
+          <t>349592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>398545</t>
+          <t>399938</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>58998</t>
+          <t>84870</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44689</t>
+          <t>66016</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>74859</t>
+          <t>106002</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>132443</t>
+          <t>71188</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69467</t>
+          <t>60079</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>250817</t>
+          <t>85207</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>191441</t>
+          <t>156058</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>128886</t>
+          <t>132335</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>321079</t>
+          <t>179794</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>372848</t>
+          <t>312039</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>372848</t>
+          <t>312039</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>372848</t>
+          <t>312039</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>612759</t>
+          <t>618924</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>612759</t>
+          <t>618924</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>612759</t>
+          <t>618924</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>44925</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>62484</t>
+          <t>70460</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>35976</t>
+          <t>34541</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25112</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55896</t>
+          <t>45609</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>80901</t>
+          <t>86704</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>69810</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>106784</t>
+          <t>108190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>212875</t>
+          <t>226746</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132263</t>
+          <t>197452</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>257106</t>
+          <t>264319</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>167782</t>
+          <t>183037</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>138831</t>
+          <t>162162</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>194212</t>
+          <t>207899</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>380657</t>
+          <t>409783</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>292344</t>
+          <t>367772</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>434061</t>
+          <t>450041</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1254560</t>
+          <t>1127097</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1138998</t>
+          <t>1077083</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1488750</t>
+          <t>1171613</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>826519</t>
+          <t>889608</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>694612</t>
+          <t>853945</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>889327</t>
+          <t>920426</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2081078</t>
+          <t>2016705</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1936708</t>
+          <t>1954331</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2367154</t>
+          <t>2071925</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>426663</t>
+          <t>492083</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>277383</t>
+          <t>447440</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>505746</t>
+          <t>534648</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>409221</t>
+          <t>376609</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>344281</t>
+          <t>345448</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>580151</t>
+          <t>407486</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>835884</t>
+          <t>868692</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>674277</t>
+          <t>815614</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>990043</t>
+          <t>922365</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1939022</t>
+          <t>1898089</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1939022</t>
+          <t>1898089</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1939022</t>
+          <t>1898089</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1439499</t>
+          <t>1483796</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1439499</t>
+          <t>1483796</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1439499</t>
+          <t>1483796</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3378520</t>
+          <t>3381885</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3378520</t>
+          <t>3381885</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3378520</t>
+          <t>3381885</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
